--- a/Sample_run/1/student/KienTTHE186727/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/KienTTHE186727/TC1/GradeDetail.xlsx
@@ -1029,7 +1029,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1088,7 +1088,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1141,7 +1141,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1197,7 +1197,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1256,7 +1256,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35914</x:v>
+        <x:v>42870</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
